--- a/product_surveys/025_hampers_collection_survey--product_surveys.xlsx
+++ b/product_surveys/025_hampers_collection_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_is_your_interest_in_hampers</t>
+          <t>What is your interest in hampers?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hamper_type</t>
+          <t>hamper_type_form_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_type_of_hampers_do_you_like</t>
+          <t>What type of hampers do you like?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hamper_size</t>
+          <t>hamper_size_form_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hamper_size</t>
+          <t>What is the size of the hamper?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hamper_color</t>
+          <t>hamper_color_form_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>favorite_hampers_color</t>
+          <t>What is your favorite hamper color?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hamper_message</t>
+          <t>hamper_price_form_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hamper_message</t>
+          <t>How much do you want to pay for the hamper?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,58 +635,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>hamper_weight_form_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>What is the weight of the hamper?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hamper_weight_range_form_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>What is the weight range of the hamper?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>hamper_weight_unit_form_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>What is the weight unit of the hamper?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>time_of_day</t>
+          <t>hamper_note_form_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time_of_day</t>
+          <t>Do you have any additional comments or notes about the hamper?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>hamper_size_form_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>What is the hamper size unit?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hamper_price</t>
+          <t>hamper_color_form_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hamper_price</t>
+          <t>What is the hamper color unit?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -773,35 +773,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hamper_weight</t>
+          <t>hamper_collection_survey_form_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hamper_weight</t>
+          <t>Additional comments or notes about the hamper?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hamper_weight_range</t>
+          <t>hamper_price_form_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hamper_weight_range</t>
+          <t>Hamper Price Form 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hamper_weight_min_max</t>
+          <t>hamper_weight_form_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hamper_weight_min_max</t>
+          <t>Hamper Weight Form 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hamper_weight_unit</t>
+          <t>hamper_weight_range_form_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hamper_weight_unit</t>
+          <t>Hamper Weight Range Form 15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hamper_size_unit</t>
+          <t>hamper_weight_unit_form_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hamper_size_unit</t>
+          <t>Hamper Weight Unit Form 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hamper_color_unit</t>
+          <t>hamper_size_unit_form_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hamper_color_unit</t>
+          <t>What is the size unit of the hamper?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,40 +906,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hamper_message</t>
+          <t>hamper_color_unit_form_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>hamper_message</t>
+          <t>What is the color unit of the hamper?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>hamper_note_form_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Hamper Note Form 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,133 +957,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>hamper_collection_survey_form_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Hamper Collection Survey Form 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>time_of_day</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>time_of_day</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>hamper_price</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>hamper_price</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>hamper_weight</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>hamper_weight</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,391 +1011,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hamper_type_choices</t>
+          <t>hamper_type_form_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hamper_type_choices</t>
+          <t>hamper_type_form_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hamper_type_choices</t>
+          <t>hamper_type_form_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'flowers'}</t>
+          <t>flowers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Flowers'}</t>
+          <t>Flowers</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hamper_size_choices</t>
+          <t>hamper_size_form_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hamper_size_choices</t>
+          <t>hamper_size_form_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hamper_size_choices</t>
+          <t>hamper_size_form_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hamper_color_choices</t>
+          <t>hamper_color_form_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hamper_color_choices</t>
+          <t>hamper_color_form_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hamper_color_choices</t>
+          <t>hamper_color_form_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hamper_weight_range_choices</t>
+          <t>hamper_weight_range_form_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less Than 10'}</t>
+          <t>Less Than 10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hamper_weight_range_choices</t>
+          <t>hamper_weight_range_form_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'10-15'}</t>
+          <t>10-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '10-15'}</t>
+          <t>10-15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hamper_weight_range_choices</t>
+          <t>hamper_weight_range_form_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_15'}</t>
+          <t>more_than_15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'More Than 15'}</t>
+          <t>More Than 15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hamper_weight_min_max_choices</t>
+          <t>hamper_weight_unit_form_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'min'}</t>
+          <t>grams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'min'}</t>
+          <t>Grams</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hamper_weight_min_max_choices</t>
+          <t>hamper_weight_unit_form_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'max'}</t>
+          <t>kilograms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'max'}</t>
+          <t>Kilograms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hamper_weight_unit_choices</t>
+          <t>hamper_weight_unit_form_8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'grams'}</t>
+          <t>pounds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Grams'}</t>
+          <t>Pounds</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hamper_weight_unit_choices</t>
+          <t>hamper_size_form_10_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'kilograms'}</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Kilograms'}</t>
+          <t>Meters</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hamper_weight_unit_choices</t>
+          <t>hamper_size_form_10_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pounds'}</t>
+          <t>kilometers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pounds'}</t>
+          <t>Kilometers</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hamper_size_unit_choices</t>
+          <t>hamper_size_form_10_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'meters'}</t>
+          <t>feet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Meters'}</t>
+          <t>Feet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hamper_size_unit_choices</t>
+          <t>hamper_color_form_11_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'kilometers'}</t>
+          <t>inches</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Kilometers'}</t>
+          <t>Inches</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hamper_size_unit_choices</t>
+          <t>hamper_color_form_11_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'feet'}</t>
+          <t>centimeters</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Feet'}</t>
+          <t>Centimeters</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hamper_color_unit_choices</t>
+          <t>hamper_color_form_11_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'inches'}</t>
+          <t>millimeters</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Inches'}</t>
+          <t>Millimeters</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hamper_color_unit_choices</t>
+          <t>hamper_weight_range_form_15_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'centimeters'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Centimeters'}</t>
+          <t>Less Than 10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hamper_color_unit_choices</t>
+          <t>hamper_weight_range_form_15_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'millimeters'}</t>
+          <t>10-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Millimeters'}</t>
+          <t>10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>hamper_weight_range_form_15_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>more_than_15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>More Than 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>hamper_weight_unit_form_16_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>grams</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Grams</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>hamper_weight_unit_form_16_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>kilograms</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kilograms</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>hamper_weight_unit_form_16_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pounds</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>hamper_size_unit_form_17_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>meters</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Meters</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>hamper_size_unit_form_17_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>kilometers</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kilometers</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>hamper_size_unit_form_17_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>feet</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>hamper_color_unit_form_18_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>inches</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Inches</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>hamper_color_unit_form_18_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>centimeters</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Centimeters</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>hamper_color_unit_form_18_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>millimeters</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Millimeters</t>
         </is>
       </c>
     </row>
